--- a/Iteration-two/IT2 Freeza - Agile Gantt chart.xlsx
+++ b/Iteration-two/IT2 Freeza - Agile Gantt chart.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DF1D40-2A15-2B4C-85D7-6BA28945849E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7B8167-0549-EB48-A0E2-CCAD0FE8AC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17140" tabRatio="415" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="59">
   <si>
     <t>Task 3</t>
   </si>
@@ -232,6 +232,24 @@
   <si>
     <t>Meeting 3</t>
   </si>
+  <si>
+    <t>Iteration 1 Completion</t>
+  </si>
+  <si>
+    <t>Iteration 2 Completion</t>
+  </si>
+  <si>
+    <t>Progress Report</t>
+  </si>
+  <si>
+    <t>Liam</t>
+  </si>
+  <si>
+    <t>Kyle</t>
+  </si>
+  <si>
+    <t>Resource Requirements</t>
+  </si>
 </sst>
 </file>
 
@@ -241,7 +259,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="d"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,6 +497,12 @@
       <sz val="14"/>
       <name val="Corbel"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -2437,7 +2461,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="30"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2718,8 +2742,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Milestones43524" displayName="Milestones43524" ref="B9:G38" totalsRowShown="0" headerRowDxfId="57">
-  <autoFilter ref="B9:G38" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Milestones43524" displayName="Milestones43524" ref="B9:G39" totalsRowShown="0" headerRowDxfId="57">
+  <autoFilter ref="B9:G39" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3339,7 +3363,7 @@
       </c>
       <c r="C6" s="80" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Milestones4352[Start])=0,TODAY(),B11(Milestones4352[Start])),TODAY())</f>
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="D6" s="81"/>
       <c r="E6" s="75"/>
@@ -3442,227 +3466,227 @@
       <c r="H7" s="83"/>
       <c r="I7" s="98">
         <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="J7" s="99">
         <f ca="1">I7+1</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="K7" s="99">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="L7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="M7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="N7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="O7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="P7" s="99">
         <f ca="1">O7+1</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="Q7" s="99">
         <f ca="1">P7+1</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="R7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="S7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="T7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="U7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="V7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="W7" s="99">
         <f ca="1">V7+1</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="X7" s="99">
         <f ca="1">W7+1</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="Y7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="Z7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="AA7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="AB7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="AC7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="AD7" s="99">
         <f ca="1">AC7+1</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="AE7" s="99">
         <f ca="1">AD7+1</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="AF7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="AG7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="AH7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="AI7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AJ7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="AK7" s="99">
         <f ca="1">AJ7+1</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AL7" s="99">
         <f ca="1">AK7+1</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="AM7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="AN7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="AO7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="AP7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="AQ7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="AR7" s="99">
         <f ca="1">AQ7+1</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="AS7" s="99">
         <f ca="1">AR7+1</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AT7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="AU7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="AV7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AW7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AX7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AY7" s="99">
         <f ca="1">AX7+1</f>
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AZ7" s="99">
         <f ca="1">AY7+1</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BA7" s="99">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BB7" s="99">
         <f t="shared" ca="1" si="1"/>
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BC7" s="99">
         <f t="shared" ca="1" si="1"/>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BD7" s="99">
         <f t="shared" ca="1" si="1"/>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BE7" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BF7" s="99">
         <f ca="1">BE7+1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BG7" s="99">
         <f ca="1">BF7+1</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BH7" s="99">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="BI7" s="99">
         <f t="shared" ca="1" si="2"/>
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="BJ7" s="99">
         <f t="shared" ca="1" si="2"/>
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="BK7" s="99">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="BL7" s="100">
         <f t="shared" ca="1" si="2"/>
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3754,15 +3778,15 @@
       <c r="H9" s="88"/>
       <c r="I9" s="106" t="str">
         <f t="shared" ref="I9:BL9" ca="1" si="3">LEFT(TEXT(I7,"ddd"),1)</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="J9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="K9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="L9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3770,27 +3794,27 @@
       </c>
       <c r="M9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="N9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="O9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="P9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="Q9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="R9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="S9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3798,27 +3822,27 @@
       </c>
       <c r="T9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="U9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="V9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="W9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="X9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="Y9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="Z9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3826,27 +3850,27 @@
       </c>
       <c r="AA9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AB9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AC9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AD9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AE9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AF9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AG9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3854,27 +3878,27 @@
       </c>
       <c r="AH9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AI9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AJ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AK9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AL9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AM9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AN9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3882,27 +3906,27 @@
       </c>
       <c r="AO9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AP9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AQ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AR9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AS9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AT9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AU9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3910,27 +3934,27 @@
       </c>
       <c r="AV9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AW9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AX9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AY9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AZ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="BA9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BB9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3938,27 +3962,27 @@
       </c>
       <c r="BC9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BD9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BE9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="BF9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="BG9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="BH9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BI9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3966,15 +3990,15 @@
       </c>
       <c r="BJ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BK9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BL9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4294,7 +4318,7 @@
       </c>
       <c r="F12" s="61">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="G12" s="62">
         <v>3</v>
@@ -4537,7 +4561,7 @@
       <c r="E13" s="60"/>
       <c r="F13" s="61">
         <f ca="1">TODAY()+5</f>
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="G13" s="62">
         <v>1</v>
@@ -4782,7 +4806,7 @@
       </c>
       <c r="F14" s="61">
         <f ca="1">F12-3</f>
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="G14" s="62">
         <v>10</v>
@@ -5025,7 +5049,7 @@
       <c r="E15" s="60"/>
       <c r="F15" s="61">
         <f ca="1">F12+20</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="G15" s="62">
         <v>1</v>
@@ -5270,7 +5294,7 @@
       </c>
       <c r="F16" s="61">
         <f ca="1">F12+6</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="G16" s="62">
         <v>6</v>
@@ -5751,7 +5775,7 @@
       </c>
       <c r="F18" s="61">
         <f ca="1">F12+6</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="G18" s="62">
         <v>13</v>
@@ -5996,7 +6020,7 @@
       </c>
       <c r="F19" s="61">
         <f ca="1">F18+2</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="G19" s="62">
         <v>9</v>
@@ -6241,7 +6265,7 @@
       </c>
       <c r="F20" s="61">
         <f ca="1">F19+5</f>
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="G20" s="62">
         <v>11</v>
@@ -6484,7 +6508,7 @@
       <c r="E21" s="60"/>
       <c r="F21" s="61">
         <f ca="1">F20+2</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="G21" s="62">
         <v>1</v>
@@ -6725,7 +6749,7 @@
       <c r="E22" s="60"/>
       <c r="F22" s="61">
         <f ca="1">F21+1</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="G22" s="62">
         <v>24</v>
@@ -7204,7 +7228,7 @@
       <c r="E24" s="60"/>
       <c r="F24" s="61">
         <f ca="1">F12+15</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="G24" s="62">
         <v>4</v>
@@ -7447,7 +7471,7 @@
       <c r="E25" s="60"/>
       <c r="F25" s="61">
         <f ca="1">F24+3</f>
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="G25" s="62">
         <v>14</v>
@@ -7690,7 +7714,7 @@
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f ca="1">F25+15</f>
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="G26" s="62">
         <v>6</v>
@@ -7933,7 +7957,7 @@
       <c r="E27" s="60"/>
       <c r="F27" s="61">
         <f ca="1">F21+22</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="G27" s="62">
         <v>3</v>
@@ -8176,7 +8200,7 @@
       <c r="E28" s="60"/>
       <c r="F28" s="61">
         <f ca="1">F16</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="G28" s="62">
         <v>19</v>
@@ -8653,7 +8677,7 @@
       <c r="E30" s="60"/>
       <c r="F30" s="61">
         <f ca="1">F27+3</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="G30" s="62">
         <v>15</v>
@@ -8894,7 +8918,7 @@
       <c r="E31" s="60"/>
       <c r="F31" s="61">
         <f ca="1">F30+14</f>
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="G31" s="62">
         <v>5</v>
@@ -9137,7 +9161,7 @@
       <c r="E32" s="60"/>
       <c r="F32" s="61">
         <f ca="1">F31+42</f>
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="G32" s="62">
         <v>1</v>
@@ -10666,7 +10690,7 @@
       </c>
       <c r="C6" s="34" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Milestones435[Start])=0,TODAY(),B11(Milestones435[Start])),TODAY())</f>
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="D6" s="53"/>
       <c r="E6" s="32"/>
@@ -10770,227 +10794,227 @@
       <c r="H7" s="29"/>
       <c r="I7" s="96">
         <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="J7" s="17">
         <f ca="1">I7+1</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="K7" s="17">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="L7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="M7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="O7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="P7" s="17">
         <f ca="1">O7+1</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="Q7" s="17">
         <f ca="1">P7+1</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="R7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="S7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="T7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="U7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="V7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="W7" s="17">
         <f ca="1">V7+1</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="X7" s="17">
         <f ca="1">W7+1</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="Y7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="Z7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="AA7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="AB7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="AC7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="AD7" s="17">
         <f ca="1">AC7+1</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="AE7" s="17">
         <f ca="1">AD7+1</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="AF7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="AG7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="AH7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="AI7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="AJ7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="AK7" s="17">
         <f ca="1">AJ7+1</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="AL7" s="17">
         <f ca="1">AK7+1</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="AM7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="AN7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="AO7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="AP7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="AQ7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="AR7" s="17">
         <f ca="1">AQ7+1</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="AS7" s="17">
         <f ca="1">AR7+1</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AT7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="AU7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="AV7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AW7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AX7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AY7" s="17">
         <f ca="1">AX7+1</f>
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="AZ7" s="17">
         <f ca="1">AY7+1</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BA7" s="17">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="BB7" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="BC7" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="BD7" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="BE7" s="64">
         <f t="shared" ca="1" si="1"/>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="BF7" s="17">
         <f ca="1">BE7+1</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="BG7" s="17">
         <f ca="1">BF7+1</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BH7" s="17">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="BI7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="BJ7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="BK7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="BL7" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="BM7" s="32"/>
     </row>
@@ -11084,15 +11108,15 @@
       <c r="H9" s="48"/>
       <c r="I9" s="37" t="str">
         <f t="shared" ref="I9:BL9" ca="1" si="3">LEFT(TEXT(I7,"ddd"),1)</f>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="J9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="K9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="L9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11100,27 +11124,27 @@
       </c>
       <c r="M9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="N9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="O9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="P9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="Q9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="R9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="S9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11128,27 +11152,27 @@
       </c>
       <c r="T9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="U9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="V9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="W9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="X9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="Y9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="Z9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11156,27 +11180,27 @@
       </c>
       <c r="AA9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AB9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AC9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AD9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AE9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AF9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AG9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11184,27 +11208,27 @@
       </c>
       <c r="AH9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AI9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AJ9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AK9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AL9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AM9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AN9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11212,27 +11236,27 @@
       </c>
       <c r="AO9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AP9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AQ9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AR9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AS9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="AT9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AU9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11240,27 +11264,27 @@
       </c>
       <c r="AV9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AW9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="AX9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AY9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AZ9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="BA9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BB9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11268,27 +11292,27 @@
       </c>
       <c r="BC9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BD9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BE9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="BF9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="BG9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="BH9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BI9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -11296,15 +11320,15 @@
       </c>
       <c r="BJ9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BK9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>T</v>
       </c>
       <c r="BL9" s="37" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="BM9" s="32"/>
     </row>
@@ -11628,7 +11652,7 @@
       </c>
       <c r="F12" s="23">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="G12" s="24">
         <v>3</v>
@@ -11872,7 +11896,7 @@
       <c r="E13" s="22"/>
       <c r="F13" s="23">
         <f ca="1">TODAY()+5</f>
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="G13" s="24">
         <v>1</v>
@@ -12118,7 +12142,7 @@
       </c>
       <c r="F14" s="23">
         <f ca="1">F12-3</f>
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="G14" s="24">
         <v>10</v>
@@ -12362,7 +12386,7 @@
       <c r="E15" s="22"/>
       <c r="F15" s="23">
         <f ca="1">F12+20</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="G15" s="24">
         <v>1</v>
@@ -12608,7 +12632,7 @@
       </c>
       <c r="F16" s="23">
         <f ca="1">F12+6</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="G16" s="24">
         <v>6</v>
@@ -13091,7 +13115,7 @@
       </c>
       <c r="F18" s="23">
         <f ca="1">F12+6</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="G18" s="24">
         <v>13</v>
@@ -13337,7 +13361,7 @@
       </c>
       <c r="F19" s="23">
         <f ca="1">F18+2</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="G19" s="24">
         <v>9</v>
@@ -13583,7 +13607,7 @@
       </c>
       <c r="F20" s="23">
         <f ca="1">F19+5</f>
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="G20" s="24">
         <v>11</v>
@@ -13827,7 +13851,7 @@
       <c r="E21" s="22"/>
       <c r="F21" s="23">
         <f ca="1">F20+2</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="G21" s="24">
         <v>1</v>
@@ -14069,7 +14093,7 @@
       <c r="E22" s="22"/>
       <c r="F22" s="23">
         <f ca="1">F21+1</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="G22" s="24">
         <v>24</v>
@@ -14550,7 +14574,7 @@
       <c r="E24" s="22"/>
       <c r="F24" s="23">
         <f ca="1">F12+15</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="G24" s="24">
         <v>4</v>
@@ -14794,7 +14818,7 @@
       <c r="E25" s="22"/>
       <c r="F25" s="23">
         <f ca="1">F24+3</f>
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="G25" s="24">
         <v>14</v>
@@ -15038,7 +15062,7 @@
       <c r="E26" s="22"/>
       <c r="F26" s="23">
         <f ca="1">F25+15</f>
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="G26" s="24">
         <v>6</v>
@@ -15282,7 +15306,7 @@
       <c r="E27" s="22"/>
       <c r="F27" s="23">
         <f ca="1">F21+22</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="G27" s="24">
         <v>3</v>
@@ -15526,7 +15550,7 @@
       <c r="E28" s="22"/>
       <c r="F28" s="23">
         <f ca="1">F16</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="G28" s="24">
         <v>19</v>
@@ -16005,7 +16029,7 @@
       <c r="E30" s="22"/>
       <c r="F30" s="23">
         <f ca="1">F27+3</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="G30" s="24">
         <v>15</v>
@@ -16247,7 +16271,7 @@
       <c r="E31" s="22"/>
       <c r="F31" s="23">
         <f ca="1">F30+14</f>
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="G31" s="24">
         <v>5</v>
@@ -16491,7 +16515,7 @@
       <c r="E32" s="22"/>
       <c r="F32" s="23">
         <f ca="1">F31+42</f>
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="G32" s="24">
         <v>1</v>
@@ -17715,7 +17739,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BP40"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="9" customWidth="1"/>
@@ -17886,7 +17910,7 @@
       <c r="H6" s="75"/>
       <c r="I6" s="91" t="str">
         <f ca="1">TEXT(I7,"mmmm")</f>
-        <v>February</v>
+        <v>March</v>
       </c>
       <c r="J6" s="91"/>
       <c r="K6" s="91"/>
@@ -17906,7 +17930,7 @@
       <c r="V6" s="91"/>
       <c r="W6" s="91" t="str">
         <f ca="1">IF(OR(TEXT(W7,"mmmm")=P6,TEXT(W7,"mmmm")=I6),"",TEXT(W7,"mmmm"))</f>
-        <v>March</v>
+        <v>April</v>
       </c>
       <c r="X6" s="91"/>
       <c r="Y6" s="91"/>
@@ -17956,7 +17980,7 @@
       <c r="BE6" s="90"/>
       <c r="BF6" s="90" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"mmmm")=AY6,TEXT(BF7,"mmmm")=AR6,TEXT(BF7,"mmmm")=AK6,TEXT(BF7,"mmmm")=AD6),"",TEXT(BF7,"mmmm"))</f>
-        <v>April</v>
+        <v>May</v>
       </c>
       <c r="BG6" s="90"/>
       <c r="BH6" s="90"/>
@@ -17971,7 +17995,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="82">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D7" s="74"/>
       <c r="E7" s="75"/>
@@ -17980,227 +18004,227 @@
       <c r="H7" s="83"/>
       <c r="I7" s="98">
         <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46070</v>
+        <v>46100</v>
       </c>
       <c r="J7" s="99">
         <f ca="1">I7+1</f>
-        <v>46071</v>
+        <v>46101</v>
       </c>
       <c r="K7" s="99">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46072</v>
+        <v>46102</v>
       </c>
       <c r="L7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46103</v>
       </c>
       <c r="M7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46074</v>
+        <v>46104</v>
       </c>
       <c r="N7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46075</v>
+        <v>46105</v>
       </c>
       <c r="O7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46076</v>
+        <v>46106</v>
       </c>
       <c r="P7" s="99">
         <f ca="1">O7+1</f>
-        <v>46077</v>
+        <v>46107</v>
       </c>
       <c r="Q7" s="99">
         <f ca="1">P7+1</f>
-        <v>46078</v>
+        <v>46108</v>
       </c>
       <c r="R7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46079</v>
+        <v>46109</v>
       </c>
       <c r="S7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46080</v>
+        <v>46110</v>
       </c>
       <c r="T7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46081</v>
+        <v>46111</v>
       </c>
       <c r="U7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46082</v>
+        <v>46112</v>
       </c>
       <c r="V7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46083</v>
+        <v>46113</v>
       </c>
       <c r="W7" s="99">
         <f ca="1">V7+1</f>
-        <v>46084</v>
+        <v>46114</v>
       </c>
       <c r="X7" s="99">
         <f ca="1">W7+1</f>
-        <v>46085</v>
+        <v>46115</v>
       </c>
       <c r="Y7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46086</v>
+        <v>46116</v>
       </c>
       <c r="Z7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46087</v>
+        <v>46117</v>
       </c>
       <c r="AA7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46088</v>
+        <v>46118</v>
       </c>
       <c r="AB7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46089</v>
+        <v>46119</v>
       </c>
       <c r="AC7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46090</v>
+        <v>46120</v>
       </c>
       <c r="AD7" s="99">
         <f ca="1">AC7+1</f>
-        <v>46091</v>
+        <v>46121</v>
       </c>
       <c r="AE7" s="99">
         <f ca="1">AD7+1</f>
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="AF7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46093</v>
+        <v>46123</v>
       </c>
       <c r="AG7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46094</v>
+        <v>46124</v>
       </c>
       <c r="AH7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46095</v>
+        <v>46125</v>
       </c>
       <c r="AI7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46096</v>
+        <v>46126</v>
       </c>
       <c r="AJ7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46097</v>
+        <v>46127</v>
       </c>
       <c r="AK7" s="99">
         <f ca="1">AJ7+1</f>
-        <v>46098</v>
+        <v>46128</v>
       </c>
       <c r="AL7" s="99">
         <f ca="1">AK7+1</f>
-        <v>46099</v>
+        <v>46129</v>
       </c>
       <c r="AM7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46100</v>
+        <v>46130</v>
       </c>
       <c r="AN7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46101</v>
+        <v>46131</v>
       </c>
       <c r="AO7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46102</v>
+        <v>46132</v>
       </c>
       <c r="AP7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46103</v>
+        <v>46133</v>
       </c>
       <c r="AQ7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46104</v>
+        <v>46134</v>
       </c>
       <c r="AR7" s="99">
         <f ca="1">AQ7+1</f>
-        <v>46105</v>
+        <v>46135</v>
       </c>
       <c r="AS7" s="99">
         <f ca="1">AR7+1</f>
-        <v>46106</v>
+        <v>46136</v>
       </c>
       <c r="AT7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46107</v>
+        <v>46137</v>
       </c>
       <c r="AU7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46108</v>
+        <v>46138</v>
       </c>
       <c r="AV7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46109</v>
+        <v>46139</v>
       </c>
       <c r="AW7" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>46110</v>
+        <v>46140</v>
       </c>
       <c r="AX7" s="100">
         <f t="shared" ca="1" si="0"/>
-        <v>46111</v>
+        <v>46141</v>
       </c>
       <c r="AY7" s="99">
         <f ca="1">AX7+1</f>
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="AZ7" s="99">
         <f ca="1">AY7+1</f>
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="BA7" s="99">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46114</v>
+        <v>46144</v>
       </c>
       <c r="BB7" s="99">
         <f t="shared" ca="1" si="1"/>
-        <v>46115</v>
+        <v>46145</v>
       </c>
       <c r="BC7" s="99">
         <f t="shared" ca="1" si="1"/>
-        <v>46116</v>
+        <v>46146</v>
       </c>
       <c r="BD7" s="99">
         <f t="shared" ca="1" si="1"/>
-        <v>46117</v>
+        <v>46147</v>
       </c>
       <c r="BE7" s="100">
         <f t="shared" ca="1" si="1"/>
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="BF7" s="99">
         <f ca="1">BE7+1</f>
-        <v>46119</v>
+        <v>46149</v>
       </c>
       <c r="BG7" s="99">
         <f ca="1">BF7+1</f>
-        <v>46120</v>
+        <v>46150</v>
       </c>
       <c r="BH7" s="99">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46121</v>
+        <v>46151</v>
       </c>
       <c r="BI7" s="99">
         <f t="shared" ca="1" si="2"/>
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="BJ7" s="99">
         <f t="shared" ca="1" si="2"/>
-        <v>46123</v>
+        <v>46153</v>
       </c>
       <c r="BK7" s="99">
         <f t="shared" ca="1" si="2"/>
-        <v>46124</v>
+        <v>46154</v>
       </c>
       <c r="BL7" s="100">
         <f t="shared" ca="1" si="2"/>
-        <v>46125</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -18296,27 +18320,27 @@
       </c>
       <c r="J9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="K9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="L9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="M9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="N9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="O9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="P9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18324,27 +18348,27 @@
       </c>
       <c r="Q9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="R9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="S9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="T9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="U9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="V9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="W9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18352,27 +18376,27 @@
       </c>
       <c r="X9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="Y9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="Z9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AA9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AB9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AC9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AD9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18380,27 +18404,27 @@
       </c>
       <c r="AE9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="AF9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="AG9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AH9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AI9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AJ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AK9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18408,27 +18432,27 @@
       </c>
       <c r="AL9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="AM9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="AN9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AO9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AP9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AQ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AR9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18436,27 +18460,27 @@
       </c>
       <c r="AS9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="AT9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="AU9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AV9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AW9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AX9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AY9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18464,27 +18488,27 @@
       </c>
       <c r="AZ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="BA9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="BB9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BC9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BD9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="BE9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="BF9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18492,27 +18516,27 @@
       </c>
       <c r="BG9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="BH9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="BI9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BJ9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BK9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="BL9" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18591,7 +18615,7 @@
       <c r="G11" s="62"/>
       <c r="H11" s="59"/>
       <c r="I11" s="26" t="str">
-        <f t="shared" ref="I11:X28" ca="1" si="4">IF(AND($C11="Goal",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1),1,""))</f>
+        <f t="shared" ref="I11:X29" ca="1" si="4">IF(AND($C11="Goal",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1),1,""))</f>
         <v/>
       </c>
       <c r="J11" s="26" t="str">
@@ -18655,7 +18679,7 @@
         <v/>
       </c>
       <c r="Y11" s="26" t="str">
-        <f t="shared" ref="Y11:AN28" ca="1" si="5">IF(AND($C11="Goal",Y$7&gt;=$F11,Y$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",Y$7&gt;=$F11,Y$7&lt;=$F11+$G11-1),1,""))</f>
+        <f t="shared" ref="Y11:AN29" ca="1" si="5">IF(AND($C11="Goal",Y$7&gt;=$F11,Y$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",Y$7&gt;=$F11,Y$7&lt;=$F11+$G11-1),1,""))</f>
         <v/>
       </c>
       <c r="Z11" s="26" t="str">
@@ -18719,7 +18743,7 @@
         <v/>
       </c>
       <c r="AO11" s="26" t="str">
-        <f t="shared" ref="AO11:BD28" ca="1" si="6">IF(AND($C11="Goal",AO$7&gt;=$F11,AO$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",AO$7&gt;=$F11,AO$7&lt;=$F11+$G11-1),1,""))</f>
+        <f t="shared" ref="AO11:BD29" ca="1" si="6">IF(AND($C11="Goal",AO$7&gt;=$F11,AO$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",AO$7&gt;=$F11,AO$7&lt;=$F11+$G11-1),1,""))</f>
         <v/>
       </c>
       <c r="AP11" s="26" t="str">
@@ -18783,7 +18807,7 @@
         <v/>
       </c>
       <c r="BE11" s="26" t="str">
-        <f t="shared" ref="BE11:BL28" ca="1" si="7">IF(AND($C11="Goal",BE$7&gt;=$F11,BE$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",BE$7&gt;=$F11,BE$7&lt;=$F11+$G11-1),1,""))</f>
+        <f t="shared" ref="BE11:BL29" ca="1" si="7">IF(AND($C11="Goal",BE$7&gt;=$F11,BE$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",BE$7&gt;=$F11,BE$7&lt;=$F11+$G11-1),1,""))</f>
         <v/>
       </c>
       <c r="BF11" s="26" t="str">
@@ -19071,7 +19095,9 @@
       <c r="C13" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="59" t="s">
+        <v>56</v>
+      </c>
       <c r="E13" s="60"/>
       <c r="F13" s="61">
         <f>C6+6</f>
@@ -19082,7 +19108,7 @@
       </c>
       <c r="H13" s="59"/>
       <c r="I13" s="26" t="str">
-        <f t="shared" ref="I13:X30" ca="1" si="8">IF(AND($C13="Goal",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),2,IF(AND($C13="Milestone",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),1,""))</f>
+        <f t="shared" ref="I13:X31" ca="1" si="8">IF(AND($C13="Goal",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),2,IF(AND($C13="Milestone",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),1,""))</f>
         <v/>
       </c>
       <c r="J13" s="26" t="str">
@@ -19105,9 +19131,9 @@
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="O13" s="26">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+      <c r="O13" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="P13" s="26" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -19356,9 +19382,9 @@
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="P14" s="26">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+      <c r="P14" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="Q14" s="26" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -19809,7 +19835,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16" s="60">
         <v>1</v>
@@ -19878,9 +19904,9 @@
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="W16" s="26">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+      <c r="W16" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="X16" s="26" t="str">
         <f t="shared" ref="X16:BD16" ca="1" si="9">IF(AND($C16="Goal",X$7&gt;=$F16,X$7&lt;=$F16+$G16-1),2,IF(AND($C16="Milestone",X$7&gt;=$F16,X$7&lt;=$F16+$G16-1),1,""))</f>
@@ -20303,7 +20329,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E18" s="60">
         <v>1</v>
@@ -20381,7 +20407,7 @@
         <v/>
       </c>
       <c r="Y18" s="26" t="str">
-        <f t="shared" ref="Y18:BD18" ca="1" si="10">IF(AND($C18="Goal",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),2,IF(AND($C18="Milestone",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),1,""))</f>
+        <f t="shared" ref="Y18:BD19" ca="1" si="10">IF(AND($C18="Goal",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),2,IF(AND($C18="Milestone",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),1,""))</f>
         <v/>
       </c>
       <c r="Z18" s="26" t="str">
@@ -20400,9 +20426,9 @@
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="AD18" s="26">
+      <c r="AD18" s="26" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v/>
       </c>
       <c r="AE18" s="26" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -20542,206 +20568,215 @@
       </c>
     </row>
     <row r="19" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
-      <c r="B19" s="116" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="59" t="s">
+        <v>41</v>
+      </c>
       <c r="E19" s="60"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="62"/>
+      <c r="F19" s="61">
+        <f>F21-1</f>
+        <v>46100</v>
+      </c>
+      <c r="G19" s="62">
+        <v>1</v>
+      </c>
       <c r="H19" s="59"/>
-      <c r="I19" s="26" t="str">
+      <c r="I19" s="26">
         <f t="shared" ca="1" si="8"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="K19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="L19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="M19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="N19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="O19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="P19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="Q19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="R19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="S19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="T19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="U19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="V19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="W19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="X19" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="Y19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="Z19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AA19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AB19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AC19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AD19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AE19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AF19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AG19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AH19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AI19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AJ19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AK19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AL19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AM19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AN19" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AO19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AP19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AQ19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AR19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AS19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AT19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AU19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AV19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AW19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AX19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AY19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="AZ19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="BA19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="BB19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="BC19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="BD19" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="BE19" s="26" t="str">
@@ -20779,23 +20814,14 @@
     </row>
     <row r="20" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10"/>
-      <c r="B20" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>13</v>
-      </c>
+      <c r="B20" s="116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="59"/>
       <c r="D20" s="59"/>
-      <c r="E20" s="60">
-        <v>0.8</v>
-      </c>
-      <c r="F20" s="61">
-        <f>DATE(2026,3,20)</f>
-        <v>46101</v>
-      </c>
-      <c r="G20" s="62">
-        <v>15</v>
-      </c>
+      <c r="E20" s="60"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="62"/>
       <c r="H20" s="59"/>
       <c r="I20" s="26" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -21023,19 +21049,21 @@
       </c>
     </row>
     <row r="21" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="59"/>
+      <c r="D21" s="59" t="s">
+        <v>45</v>
+      </c>
       <c r="E21" s="60">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="F21" s="61">
-        <f>F20</f>
+        <f>DATE(2026,3,20)</f>
         <v>46101</v>
       </c>
       <c r="G21" s="62">
@@ -21270,505 +21298,517 @@
     <row r="22" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="63" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="59"/>
+        <v>13</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>57</v>
+      </c>
       <c r="E22" s="60">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="F22" s="61">
-        <f t="shared" ref="F22:F24" si="11">F21</f>
-        <v>46101</v>
+        <f>F21+14</f>
+        <v>46115</v>
       </c>
       <c r="G22" s="62">
         <v>15</v>
       </c>
       <c r="H22" s="59"/>
       <c r="I22" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f ca="1">IF(AND($C22="Goal",I$7&gt;=$F22,I$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",I$7&gt;=$F22,I$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="J22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",J$7&gt;=$F22,J$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",J$7&gt;=$F22,J$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="K22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",K$7&gt;=$F22,K$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",K$7&gt;=$F22,K$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="L22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",L$7&gt;=$F22,L$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",L$7&gt;=$F22,L$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="M22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",M$7&gt;=$F22,M$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",M$7&gt;=$F22,M$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="N22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",N$7&gt;=$F22,N$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",N$7&gt;=$F22,N$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="O22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",O$7&gt;=$F22,O$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",O$7&gt;=$F22,O$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="P22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",P$7&gt;=$F22,P$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",P$7&gt;=$F22,P$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="Q22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",Q$7&gt;=$F22,Q$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",Q$7&gt;=$F22,Q$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="R22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",R$7&gt;=$F22,R$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",R$7&gt;=$F22,R$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="S22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",S$7&gt;=$F22,S$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",S$7&gt;=$F22,S$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="T22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",T$7&gt;=$F22,T$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",T$7&gt;=$F22,T$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="U22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",U$7&gt;=$F22,U$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",U$7&gt;=$F22,U$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="V22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",V$7&gt;=$F22,V$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",V$7&gt;=$F22,V$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="W22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",W$7&gt;=$F22,W$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",W$7&gt;=$F22,W$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="X22" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C22="Goal",X$7&gt;=$F22,X$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",X$7&gt;=$F22,X$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="Y22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",Y$7&gt;=$F22,Y$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",Y$7&gt;=$F22,Y$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="Z22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",Z$7&gt;=$F22,Z$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",Z$7&gt;=$F22,Z$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AA22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AA$7&gt;=$F22,AA$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AA$7&gt;=$F22,AA$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AB22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AB$7&gt;=$F22,AB$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AB$7&gt;=$F22,AB$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AC22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AC$7&gt;=$F22,AC$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AC$7&gt;=$F22,AC$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AD22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AD$7&gt;=$F22,AD$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AD$7&gt;=$F22,AD$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AE22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AE$7&gt;=$F22,AE$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AE$7&gt;=$F22,AE$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AF22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AF$7&gt;=$F22,AF$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AF$7&gt;=$F22,AF$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AG22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AG$7&gt;=$F22,AG$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AG$7&gt;=$F22,AG$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AH22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AH$7&gt;=$F22,AH$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AH$7&gt;=$F22,AH$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AI22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AI$7&gt;=$F22,AI$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AI$7&gt;=$F22,AI$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AJ22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AJ$7&gt;=$F22,AJ$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AJ$7&gt;=$F22,AJ$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AK22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AK$7&gt;=$F22,AK$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AK$7&gt;=$F22,AK$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AL22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AL$7&gt;=$F22,AL$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AL$7&gt;=$F22,AL$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AM22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AM$7&gt;=$F22,AM$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AM$7&gt;=$F22,AM$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AN22" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C22="Goal",AN$7&gt;=$F22,AN$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AN$7&gt;=$F22,AN$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AO22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AO$7&gt;=$F22,AO$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AO$7&gt;=$F22,AO$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AP22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AP$7&gt;=$F22,AP$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AP$7&gt;=$F22,AP$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AQ22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AQ$7&gt;=$F22,AQ$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AQ$7&gt;=$F22,AQ$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AR22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AR$7&gt;=$F22,AR$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AR$7&gt;=$F22,AR$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AS22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AS$7&gt;=$F22,AS$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AS$7&gt;=$F22,AS$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AT22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AT$7&gt;=$F22,AT$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AT$7&gt;=$F22,AT$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AU22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AU$7&gt;=$F22,AU$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AU$7&gt;=$F22,AU$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AV22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AV$7&gt;=$F22,AV$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AV$7&gt;=$F22,AV$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AW22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AW$7&gt;=$F22,AW$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AW$7&gt;=$F22,AW$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AX22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AX$7&gt;=$F22,AX$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AX$7&gt;=$F22,AX$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AY22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AY$7&gt;=$F22,AY$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AY$7&gt;=$F22,AY$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="AZ22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",AZ$7&gt;=$F22,AZ$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",AZ$7&gt;=$F22,AZ$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BA22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",BA$7&gt;=$F22,BA$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BA$7&gt;=$F22,BA$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BB22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",BB$7&gt;=$F22,BB$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BB$7&gt;=$F22,BB$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BC22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",BC$7&gt;=$F22,BC$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BC$7&gt;=$F22,BC$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BD22" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C22="Goal",BD$7&gt;=$F22,BD$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BD$7&gt;=$F22,BD$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BE22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BE$7&gt;=$F22,BE$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BE$7&gt;=$F22,BE$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BF22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BF$7&gt;=$F22,BF$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BF$7&gt;=$F22,BF$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BG22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BG$7&gt;=$F22,BG$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BG$7&gt;=$F22,BG$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BH22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BH$7&gt;=$F22,BH$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BH$7&gt;=$F22,BH$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BI22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BI$7&gt;=$F22,BI$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BI$7&gt;=$F22,BI$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BJ22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BJ$7&gt;=$F22,BJ$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BJ$7&gt;=$F22,BJ$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BK22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BK$7&gt;=$F22,BK$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BK$7&gt;=$F22,BK$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
       <c r="BL22" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C22="Goal",BL$7&gt;=$F22,BL$7&lt;=$F22+$G22-1),2,IF(AND($C22="Milestone",BL$7&gt;=$F22,BL$7&lt;=$F22+$G22-1),1,""))</f>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="63" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="60"/>
+        <v>13</v>
+      </c>
+      <c r="D23" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="60">
+        <v>0.7</v>
+      </c>
       <c r="F23" s="61">
-        <f t="shared" si="11"/>
-        <v>46101</v>
+        <f>F22+10</f>
+        <v>46125</v>
       </c>
       <c r="G23" s="62">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H23" s="59"/>
       <c r="I23" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f ca="1">IF(AND($C23="Goal",I$7&gt;=$F23,I$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",I$7&gt;=$F23,I$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="J23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",J$7&gt;=$F23,J$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",J$7&gt;=$F23,J$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="K23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",K$7&gt;=$F23,K$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",K$7&gt;=$F23,K$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="L23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",L$7&gt;=$F23,L$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",L$7&gt;=$F23,L$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="M23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",M$7&gt;=$F23,M$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",M$7&gt;=$F23,M$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="N23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",N$7&gt;=$F23,N$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",N$7&gt;=$F23,N$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="O23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",O$7&gt;=$F23,O$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",O$7&gt;=$F23,O$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="P23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",P$7&gt;=$F23,P$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",P$7&gt;=$F23,P$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="Q23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",Q$7&gt;=$F23,Q$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",Q$7&gt;=$F23,Q$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="R23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",R$7&gt;=$F23,R$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",R$7&gt;=$F23,R$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="S23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",S$7&gt;=$F23,S$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",S$7&gt;=$F23,S$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="T23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",T$7&gt;=$F23,T$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",T$7&gt;=$F23,T$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="U23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",U$7&gt;=$F23,U$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",U$7&gt;=$F23,U$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="V23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",V$7&gt;=$F23,V$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",V$7&gt;=$F23,V$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="W23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",W$7&gt;=$F23,W$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",W$7&gt;=$F23,W$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="X23" s="26" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(AND($C23="Goal",X$7&gt;=$F23,X$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",X$7&gt;=$F23,X$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="Y23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",Y$7&gt;=$F23,Y$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",Y$7&gt;=$F23,Y$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="Z23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",Z$7&gt;=$F23,Z$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",Z$7&gt;=$F23,Z$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AA23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AA$7&gt;=$F23,AA$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AA$7&gt;=$F23,AA$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AB23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AB$7&gt;=$F23,AB$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AB$7&gt;=$F23,AB$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AC23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AC$7&gt;=$F23,AC$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AC$7&gt;=$F23,AC$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AD23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AD$7&gt;=$F23,AD$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AD$7&gt;=$F23,AD$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AE23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AE$7&gt;=$F23,AE$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AE$7&gt;=$F23,AE$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AF23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AF$7&gt;=$F23,AF$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AF$7&gt;=$F23,AF$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AG23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AG$7&gt;=$F23,AG$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AG$7&gt;=$F23,AG$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AH23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AH$7&gt;=$F23,AH$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AH$7&gt;=$F23,AH$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AI23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AI$7&gt;=$F23,AI$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AI$7&gt;=$F23,AI$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AJ23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AJ$7&gt;=$F23,AJ$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AJ$7&gt;=$F23,AJ$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AK23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AK$7&gt;=$F23,AK$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AK$7&gt;=$F23,AK$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AL23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(AND($C23="Goal",AL$7&gt;=$F23,AL$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AL$7&gt;=$F23,AL$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AM23" s="26" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN23" s="26">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <f ca="1">IF(AND($C23="Goal",AM$7&gt;=$F23,AM$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AM$7&gt;=$F23,AM$7&lt;=$F23+$G23-1),1,""))</f>
+        <v/>
+      </c>
+      <c r="AN23" s="26" t="str">
+        <f ca="1">IF(AND($C23="Goal",AN$7&gt;=$F23,AN$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AN$7&gt;=$F23,AN$7&lt;=$F23+$G23-1),1,""))</f>
+        <v/>
       </c>
       <c r="AO23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AO$7&gt;=$F23,AO$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AO$7&gt;=$F23,AO$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AP23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AP$7&gt;=$F23,AP$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AP$7&gt;=$F23,AP$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AQ23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AQ$7&gt;=$F23,AQ$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AQ$7&gt;=$F23,AQ$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AR23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AR$7&gt;=$F23,AR$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AR$7&gt;=$F23,AR$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AS23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AS$7&gt;=$F23,AS$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AS$7&gt;=$F23,AS$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AT23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AT$7&gt;=$F23,AT$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AT$7&gt;=$F23,AT$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AU23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AU$7&gt;=$F23,AU$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AU$7&gt;=$F23,AU$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AV23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AV$7&gt;=$F23,AV$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AV$7&gt;=$F23,AV$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AW23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AW$7&gt;=$F23,AW$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AW$7&gt;=$F23,AW$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AX23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AX$7&gt;=$F23,AX$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AX$7&gt;=$F23,AX$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AY23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AY$7&gt;=$F23,AY$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AY$7&gt;=$F23,AY$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="AZ23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",AZ$7&gt;=$F23,AZ$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",AZ$7&gt;=$F23,AZ$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BA23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",BA$7&gt;=$F23,BA$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BA$7&gt;=$F23,BA$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BB23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",BB$7&gt;=$F23,BB$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BB$7&gt;=$F23,BB$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BC23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",BC$7&gt;=$F23,BC$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BC$7&gt;=$F23,BC$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BD23" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(AND($C23="Goal",BD$7&gt;=$F23,BD$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BD$7&gt;=$F23,BD$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BE23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BE$7&gt;=$F23,BE$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BE$7&gt;=$F23,BE$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BF23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BF$7&gt;=$F23,BF$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BF$7&gt;=$F23,BF$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BG23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BG$7&gt;=$F23,BG$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BG$7&gt;=$F23,BG$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BH23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BH$7&gt;=$F23,BH$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BH$7&gt;=$F23,BH$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BI23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BI$7&gt;=$F23,BI$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BI$7&gt;=$F23,BI$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BJ23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BJ$7&gt;=$F23,BJ$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BJ$7&gt;=$F23,BJ$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BK23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BK$7&gt;=$F23,BK$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BK$7&gt;=$F23,BK$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
       <c r="BL23" s="26" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">IF(AND($C23="Goal",BL$7&gt;=$F23,BL$7&lt;=$F23+$G23-1),2,IF(AND($C23="Milestone",BL$7&gt;=$F23,BL$7&lt;=$F23+$G23-1),1,""))</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="60"/>
+        <v>55</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="60">
+        <v>0.1</v>
+      </c>
       <c r="F24" s="61">
-        <f t="shared" si="11"/>
-        <v>46101</v>
+        <f>DATE(2026,4,22)</f>
+        <v>46134</v>
       </c>
       <c r="G24" s="62">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H24" s="59"/>
       <c r="I24" s="26" t="str">
@@ -21998,14 +22038,23 @@
     </row>
     <row r="25" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
-      <c r="B25" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
+      <c r="B25" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>41</v>
+      </c>
       <c r="E25" s="60"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="62"/>
+      <c r="F25" s="61">
+        <f>DATE(2026,4,29)</f>
+        <v>46141</v>
+      </c>
+      <c r="G25" s="62">
+        <v>1</v>
+      </c>
       <c r="H25" s="59"/>
       <c r="I25" s="26" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -22171,9 +22220,9 @@
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="AX25" s="26" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
+      <c r="AX25" s="26">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="AY25" s="26" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -22234,21 +22283,14 @@
     </row>
     <row r="26" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
-      <c r="B26" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="59" t="s">
-        <v>16</v>
-      </c>
+      <c r="B26" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="59"/>
       <c r="D26" s="59"/>
       <c r="E26" s="60"/>
-      <c r="F26" s="61">
-        <f>F12+15</f>
-        <v>46085</v>
-      </c>
-      <c r="G26" s="62">
-        <v>4</v>
-      </c>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
       <c r="H26" s="59"/>
       <c r="I26" s="26" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -22478,19 +22520,19 @@
     <row r="27" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="63" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D27" s="59"/>
       <c r="E27" s="60"/>
       <c r="F27" s="61">
-        <f>F26+3</f>
-        <v>46088</v>
+        <f>F12+15</f>
+        <v>46085</v>
       </c>
       <c r="G27" s="62">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H27" s="59"/>
       <c r="I27" s="26" t="str">
@@ -22721,19 +22763,19 @@
     <row r="28" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="63" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C28" s="59" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D28" s="59"/>
       <c r="E28" s="60"/>
       <c r="F28" s="61">
-        <f>F27+15</f>
-        <v>46103</v>
+        <f>F27+3</f>
+        <v>46088</v>
       </c>
       <c r="G28" s="62">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H28" s="59"/>
       <c r="I28" s="26" t="str">
@@ -22861,7 +22903,7 @@
         <v/>
       </c>
       <c r="AN28" s="26" t="str">
-        <f t="shared" ref="AN28:BC37" ca="1" si="12">IF(AND($C28="Goal",AN$7&gt;=$F28,AN$7&lt;=$F28+$G28-1),2,IF(AND($C28="Milestone",AN$7&gt;=$F28,AN$7&lt;=$F28+$G28-1),1,""))</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AO28" s="26" t="str">
@@ -22925,7 +22967,7 @@
         <v/>
       </c>
       <c r="BD28" s="26" t="str">
-        <f t="shared" ref="BD28:BL37" ca="1" si="13">IF(AND($C28="Goal",BD$7&gt;=$F28,BD$7&lt;=$F28+$G28-1),2,IF(AND($C28="Milestone",BD$7&gt;=$F28,BD$7&lt;=$F28+$G28-1),1,""))</f>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="BE28" s="26" t="str">
@@ -22964,19 +23006,19 @@
     <row r="29" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="63" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="59" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D29" s="59"/>
       <c r="E29" s="60"/>
       <c r="F29" s="61">
-        <f>F23+22</f>
-        <v>46123</v>
+        <f>F28+15</f>
+        <v>46103</v>
       </c>
       <c r="G29" s="62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H29" s="59"/>
       <c r="I29" s="26" t="str">
@@ -22984,242 +23026,242 @@
         <v/>
       </c>
       <c r="J29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="K29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="N29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="O29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="P29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="Q29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="R29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="S29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="T29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="U29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="V29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="W29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="X29" s="26" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="Y29" s="26" t="str">
-        <f t="shared" ref="Y29:AM37" ca="1" si="14">IF(AND($C29="Goal",Y$7&gt;=$F29,Y$7&lt;=$F29+$G29-1),2,IF(AND($C29="Milestone",Y$7&gt;=$F29,Y$7&lt;=$F29+$G29-1),1,""))</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="Z29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AA29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AB29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AC29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AD29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AE29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AF29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AG29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AH29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AI29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AJ29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AK29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AL29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AM29" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="AN29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ref="AN29:BC38" ca="1" si="11">IF(AND($C29="Goal",AN$7&gt;=$F29,AN$7&lt;=$F29+$G29-1),2,IF(AND($C29="Milestone",AN$7&gt;=$F29,AN$7&lt;=$F29+$G29-1),1,""))</f>
         <v/>
       </c>
       <c r="AO29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AP29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AQ29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AR29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AS29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AT29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AU29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AV29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AW29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AX29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AY29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="AZ29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="BA29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="BB29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="BC29" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
       <c r="BD29" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ref="BD29:BL38" ca="1" si="12">IF(AND($C29="Goal",BD$7&gt;=$F29,BD$7&lt;=$F29+$G29-1),2,IF(AND($C29="Milestone",BD$7&gt;=$F29,BD$7&lt;=$F29+$G29-1),1,""))</f>
         <v/>
       </c>
       <c r="BE29" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="BF29" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="BG29" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="BH29" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="BI29" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="BJ29" s="26">
-        <f t="shared" ca="1" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="BK29" s="26">
-        <f t="shared" ca="1" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="BL29" s="26">
-        <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="BJ29" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="BK29" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="BL29" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="63" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D30" s="59"/>
       <c r="E30" s="60"/>
       <c r="F30" s="61">
-        <f>F17</f>
-        <v>46076</v>
+        <f>F24+22</f>
+        <v>46156</v>
       </c>
       <c r="G30" s="62">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H30" s="59"/>
       <c r="I30" s="26" t="str">
@@ -23287,1367 +23329,1374 @@
         <v/>
       </c>
       <c r="Y30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ref="Y30:AM38" ca="1" si="13">IF(AND($C30="Goal",Y$7&gt;=$F30,Y$7&lt;=$F30+$G30-1),2,IF(AND($C30="Milestone",Y$7&gt;=$F30,Y$7&lt;=$F30+$G30-1),1,""))</f>
         <v/>
       </c>
       <c r="Z30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM30" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC30" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL30" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
-      <c r="B31" s="116" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="59"/>
+      <c r="B31" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="59" t="s">
+        <v>14</v>
+      </c>
       <c r="D31" s="59"/>
       <c r="E31" s="60"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="62"/>
+      <c r="F31" s="61">
+        <f>F17</f>
+        <v>46076</v>
+      </c>
+      <c r="G31" s="62">
+        <v>19</v>
+      </c>
       <c r="H31" s="59"/>
       <c r="I31" s="26" t="str">
-        <f t="shared" ref="I31:X37" ca="1" si="15">IF(AND($C31="Goal",I$7&gt;=$F31,I$7&lt;=$F31+$G31-1),2,IF(AND($C31="Milestone",I$7&gt;=$F31,I$7&lt;=$F31+$G31-1),1,""))</f>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="J31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="K31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="L31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="M31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="N31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="O31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="P31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="Q31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="R31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="S31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="T31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="U31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="V31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="W31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="X31" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="Y31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="Z31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM31" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC31" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL31" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:64" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
-      <c r="B32" s="63" t="s">
-        <v>3</v>
+      <c r="B32" s="116" t="s">
+        <v>33</v>
       </c>
       <c r="C32" s="59"/>
       <c r="D32" s="59"/>
       <c r="E32" s="60"/>
-      <c r="F32" s="61">
-        <f>F29+3</f>
-        <v>46126</v>
-      </c>
-      <c r="G32" s="62">
-        <v>15</v>
-      </c>
+      <c r="F32" s="61"/>
+      <c r="G32" s="62"/>
       <c r="H32" s="59"/>
       <c r="I32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="I32:X38" ca="1" si="14">IF(AND($C32="Goal",I$7&gt;=$F32,I$7&lt;=$F32+$G32-1),2,IF(AND($C32="Milestone",I$7&gt;=$F32,I$7&lt;=$F32+$G32-1),1,""))</f>
         <v/>
       </c>
       <c r="J32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="K32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="L32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="M32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="N32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="O32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="P32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Q32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="R32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="S32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="T32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="U32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="V32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="W32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="X32" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Y32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="Z32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM32" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC32" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL32" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
       <c r="B33" s="63" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" s="59"/>
       <c r="D33" s="59"/>
       <c r="E33" s="60"/>
       <c r="F33" s="61">
-        <f>F32+14</f>
-        <v>46140</v>
+        <f>F30+3</f>
+        <v>46159</v>
       </c>
       <c r="G33" s="62">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H33" s="59"/>
       <c r="I33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="J33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="K33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="L33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="M33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="N33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="O33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="P33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Q33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="R33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="S33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="T33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="U33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="V33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="W33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="X33" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Y33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="Z33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM33" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC33" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL33" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9"/>
       <c r="B34" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="59" t="s">
-        <v>9</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C34" s="59"/>
       <c r="D34" s="59"/>
       <c r="E34" s="60"/>
       <c r="F34" s="61">
-        <f>F33+42</f>
-        <v>46182</v>
+        <f>F33+14</f>
+        <v>46173</v>
       </c>
       <c r="G34" s="62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H34" s="59"/>
       <c r="I34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="J34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="K34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="L34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="M34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="N34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="O34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="P34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Q34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="R34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="S34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="T34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="U34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="V34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="W34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="X34" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Y34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="Z34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM34" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC34" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL34" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9"/>
       <c r="B35" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="59"/>
+        <v>0</v>
+      </c>
+      <c r="C35" s="59" t="s">
+        <v>9</v>
+      </c>
       <c r="D35" s="59"/>
       <c r="E35" s="60"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="62"/>
+      <c r="F35" s="61">
+        <f>F34+42</f>
+        <v>46215</v>
+      </c>
+      <c r="G35" s="62">
+        <v>1</v>
+      </c>
       <c r="H35" s="59"/>
       <c r="I35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="J35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="K35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="L35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="M35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="N35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="O35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="P35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Q35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="R35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="S35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="T35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="U35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="V35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="W35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="X35" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Y35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="Z35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM35" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC35" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL35" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9"/>
       <c r="B36" s="63" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="59"/>
       <c r="D36" s="59"/>
@@ -24656,233 +24705,235 @@
       <c r="G36" s="62"/>
       <c r="H36" s="59"/>
       <c r="I36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="J36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="K36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="L36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="M36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="N36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="O36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="P36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Q36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="R36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="S36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="T36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="U36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="V36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="W36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="X36" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Y36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="Z36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM36" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC36" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL36" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9"/>
-      <c r="B37" s="63"/>
+      <c r="B37" s="63" t="s">
+        <v>2</v>
+      </c>
       <c r="C37" s="59"/>
       <c r="D37" s="59"/>
       <c r="E37" s="60"/>
@@ -24890,306 +24941,540 @@
       <c r="G37" s="62"/>
       <c r="H37" s="59"/>
       <c r="I37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="J37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="K37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="L37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="M37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="N37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="O37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="P37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Q37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="R37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="S37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="T37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="U37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="V37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="W37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="X37" s="26" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="Y37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="Z37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AA37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AB37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AC37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AD37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AE37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AF37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AG37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AH37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AI37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AJ37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AK37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AL37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AM37" s="26" t="str">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="AN37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AO37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AP37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AQ37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AR37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AS37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AT37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AU37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AV37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AW37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AX37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AY37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="AZ37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BA37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BB37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BC37" s="26" t="str">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="BD37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BE37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BF37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BG37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BH37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BI37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BJ37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BK37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="BL37" s="26" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="BM37" s="89"/>
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="38" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="10"/>
-      <c r="B38" s="118" t="s">
-        <v>20</v>
-      </c>
+      <c r="A38" s="9"/>
+      <c r="B38" s="63"/>
       <c r="C38" s="59"/>
       <c r="D38" s="59"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="86"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
       <c r="H38" s="59"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="87"/>
-      <c r="N38" s="87"/>
-      <c r="O38" s="87"/>
-      <c r="P38" s="87"/>
-      <c r="Q38" s="87"/>
-      <c r="R38" s="87"/>
-      <c r="S38" s="87"/>
-      <c r="T38" s="87"/>
-      <c r="U38" s="87"/>
-      <c r="V38" s="87"/>
-      <c r="W38" s="87"/>
-      <c r="X38" s="87"/>
-      <c r="Y38" s="87"/>
-      <c r="Z38" s="87"/>
-      <c r="AA38" s="87"/>
-      <c r="AB38" s="87"/>
-      <c r="AC38" s="87"/>
-      <c r="AD38" s="87"/>
-      <c r="AE38" s="87"/>
-      <c r="AF38" s="87"/>
-      <c r="AG38" s="87"/>
-      <c r="AH38" s="87"/>
-      <c r="AI38" s="87"/>
-      <c r="AJ38" s="87"/>
-      <c r="AK38" s="87"/>
-      <c r="AL38" s="87"/>
-      <c r="AM38" s="87"/>
-      <c r="AN38" s="87"/>
-      <c r="AO38" s="87"/>
-      <c r="AP38" s="87"/>
-      <c r="AQ38" s="87"/>
-      <c r="AR38" s="87"/>
-      <c r="AS38" s="87"/>
-      <c r="AT38" s="87"/>
-      <c r="AU38" s="87"/>
-      <c r="AV38" s="87"/>
-      <c r="AW38" s="87"/>
-      <c r="AX38" s="87"/>
-      <c r="AY38" s="87"/>
-      <c r="AZ38" s="87"/>
-      <c r="BA38" s="87"/>
-      <c r="BB38" s="87"/>
-      <c r="BC38" s="87"/>
-      <c r="BD38" s="87"/>
-      <c r="BE38" s="87"/>
-      <c r="BF38" s="87"/>
-      <c r="BG38" s="87"/>
-      <c r="BH38" s="87"/>
-      <c r="BI38" s="87"/>
-      <c r="BJ38" s="87"/>
-      <c r="BK38" s="87"/>
-      <c r="BL38" s="87"/>
+      <c r="I38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="J38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="K38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="L38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="M38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="N38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="O38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="P38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="Q38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="R38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="S38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="T38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="U38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="V38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="W38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="X38" s="26" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="Y38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="Z38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AA38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AB38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AC38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AD38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AE38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AF38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AG38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AH38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AI38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AJ38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AK38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AL38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AM38" s="26" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v/>
+      </c>
+      <c r="AN38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AO38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AP38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AQ38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AR38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AS38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AT38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AU38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AV38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AW38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AX38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AY38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AZ38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="BA38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="BB38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="BC38" s="26" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="BD38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BE38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BF38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BG38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BH38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BI38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BJ38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BK38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BL38" s="26" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="BM38" s="89"/>
     </row>
-    <row r="39" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="4"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="3"/>
+    <row r="39" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="10"/>
+      <c r="B39" s="118" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="87"/>
+      <c r="J39" s="87"/>
+      <c r="K39" s="87"/>
+      <c r="L39" s="87"/>
+      <c r="M39" s="87"/>
+      <c r="N39" s="87"/>
+      <c r="O39" s="87"/>
+      <c r="P39" s="87"/>
+      <c r="Q39" s="87"/>
+      <c r="R39" s="87"/>
+      <c r="S39" s="87"/>
+      <c r="T39" s="87"/>
+      <c r="U39" s="87"/>
+      <c r="V39" s="87"/>
+      <c r="W39" s="87"/>
+      <c r="X39" s="87"/>
+      <c r="Y39" s="87"/>
+      <c r="Z39" s="87"/>
+      <c r="AA39" s="87"/>
+      <c r="AB39" s="87"/>
+      <c r="AC39" s="87"/>
+      <c r="AD39" s="87"/>
+      <c r="AE39" s="87"/>
+      <c r="AF39" s="87"/>
+      <c r="AG39" s="87"/>
+      <c r="AH39" s="87"/>
+      <c r="AI39" s="87"/>
+      <c r="AJ39" s="87"/>
+      <c r="AK39" s="87"/>
+      <c r="AL39" s="87"/>
+      <c r="AM39" s="87"/>
+      <c r="AN39" s="87"/>
+      <c r="AO39" s="87"/>
+      <c r="AP39" s="87"/>
+      <c r="AQ39" s="87"/>
+      <c r="AR39" s="87"/>
+      <c r="AS39" s="87"/>
+      <c r="AT39" s="87"/>
+      <c r="AU39" s="87"/>
+      <c r="AV39" s="87"/>
+      <c r="AW39" s="87"/>
+      <c r="AX39" s="87"/>
+      <c r="AY39" s="87"/>
+      <c r="AZ39" s="87"/>
+      <c r="BA39" s="87"/>
+      <c r="BB39" s="87"/>
+      <c r="BC39" s="87"/>
+      <c r="BD39" s="87"/>
+      <c r="BE39" s="87"/>
+      <c r="BF39" s="87"/>
+      <c r="BG39" s="87"/>
+      <c r="BH39" s="87"/>
+      <c r="BI39" s="87"/>
+      <c r="BJ39" s="87"/>
+      <c r="BK39" s="87"/>
+      <c r="BL39" s="87"/>
     </row>
     <row r="40" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D40" s="5"/>
+      <c r="D40" s="4"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -25202,7 +25487,8 @@
     <mergeCell ref="N4:Q4"/>
     <mergeCell ref="S4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E38">
+  <phoneticPr fontId="34" type="noConversion"/>
+  <conditionalFormatting sqref="E9:E39">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -25226,12 +25512,12 @@
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:BL38">
+  <conditionalFormatting sqref="I7:BL39">
     <cfRule type="expression" dxfId="11" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:BL37">
+  <conditionalFormatting sqref="I10:BL38">
     <cfRule type="expression" dxfId="10" priority="7" stopIfTrue="1">
       <formula>AND($C10="Low Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
@@ -25248,7 +25534,7 @@
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I38:BL38">
+  <conditionalFormatting sqref="I39:BL39">
     <cfRule type="expression" dxfId="5" priority="13" stopIfTrue="1">
       <formula>AND(#REF!="Low Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
@@ -25274,14 +25560,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C11" xr:uid="{2A71DF35-3E17-4EA3-9F65-3869ED6D651B}">
       <formula1>"Goal,Milestone,On Track, Low Risk, Med Risk, High Risk"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 C12:C37" xr:uid="{A8CFFA66-BA13-4963-ABE3-DD76F5716C76}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 C12:C38" xr:uid="{A8CFFA66-BA13-4963-ABE3-DD76F5716C76}">
       <formula1>"Goal,Milestone,On Track, Low Risk, Med Risk, High Risk"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Scrolling Increment" prompt="Changing this number will scroll the Gantt Chart view." sqref="C7" xr:uid="{86087FA1-35BE-457A-912C-7FF26BCE687A}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This is an empty row" sqref="A37" xr:uid="{008E5CA1-A949-4186-A5FB-74F6E9478170}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Gantt milestone data. DO NOT enter anything in this row. _x000a_To add more items, insert new rows above this one._x000a_" sqref="A38" xr:uid="{CEB624D0-0F11-44F9-B89D-CE4F5F747510}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This is an empty row" sqref="A38" xr:uid="{008E5CA1-A949-4186-A5FB-74F6E9478170}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Gantt milestone data. DO NOT enter anything in this row. _x000a_To add more items, insert new rows above this one._x000a_" sqref="A39" xr:uid="{CEB624D0-0F11-44F9-B89D-CE4F5F747510}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Project information starting in cell B11 through cell G11. _x000a_Enter Milestone Description, select a Category, assign someone to the task, and enter the progress, start date, and number of days for the task to start charting._x000a_" sqref="A11" xr:uid="{6BCA7D1C-2B33-4267-B02B-4DBA8944EFBD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row contains headers for the project schedule.  B9 through G9 contains schedule information.  Cells I9 through BL9 contain the first letter of each day of the week for the date above that heading._x000a_All project timeline charting is auto generated." sqref="A9" xr:uid="{B8D2B96F-34FD-4F20-9F50-24DB43B4F207}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="A scrollbar is in cells I8 through BL8. _x000a_To jump forward or backward in the timeline, enter a value of 0 or higher in cell C7._x000a_A value of 0 takes you to the beginning of the chart." sqref="A8" xr:uid="{74A0C51E-7215-45D6-BD24-C245B7BE27E3}"/>
@@ -25349,7 +25635,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E9:E38</xm:sqref>
+          <xm:sqref>E9:E39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="6" id="{67763332-2AE9-4F93-8BB7-5ECDB6B99BA2}">
@@ -25368,7 +25654,7 @@
               <x14:cfIcon iconSet="3Signs" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I10:BL37</xm:sqref>
+          <xm:sqref>I10:BL38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="12" id="{5AD67FB9-23B4-4F54-BD80-7A6CF9720346}">
@@ -25387,7 +25673,7 @@
               <x14:cfIcon iconSet="3Signs" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I38:BL38</xm:sqref>
+          <xm:sqref>I39:BL39</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -25396,34 +25682,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22a266b9fa9a230c5a512669d8b298c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eddc33fff6b14141ee5c74a0d29ea6a1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -25699,27 +25957,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C87518-DD8E-42CD-8DAC-291A323E849B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25738,4 +26004,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>